--- a/UyumsuzluklarTarama_Gunluk_131026.xlsx
+++ b/UyumsuzluklarTarama_Gunluk_131026.xlsx
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b), OBV:DİRENÇ↑(2b)</t>
+          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.56</v>
+        <v>42.44</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b), OBV:DİRENÇ↑(2b)</t>
+          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b)</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <t>CCI:DESTEK↓, OBV:DESTEK↓</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑(1b), CCI:DESTEK↓, Chaikin:DİRENÇ↑(1b), MOM:DİRENÇ↑(1b), ROC:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(2b)</t>
+          <t>ATR:DİRENÇ↑(1b), CCI:DESTEK↓, Chaikin:DİRENÇ↑(1b), MOM:DİRENÇ↑(1b), OBV:DESTEK↓, ROC:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(2b)</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.56</v>
+        <v>42.44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.42</v>
+        <v>18.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.64</v>
+        <v>12.77</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>230.3</v>
+        <v>231</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>230.3</v>
+        <v>231</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12.64</v>
+        <v>12.77</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42.56</v>
+        <v>42.44</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18.42</v>
+        <v>18.55</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.92</v>
+        <v>24.96</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.56</v>
+        <v>42.44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.42</v>
+        <v>18.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.64</v>
+        <v>12.77</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>230.3</v>
+        <v>231</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>

--- a/UyumsuzluklarTarama_Gunluk_131026.xlsx
+++ b/UyumsuzluklarTarama_Gunluk_131026.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taze_Sinyaller" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugun'!$A$1:$O$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tum_Sonuclar'!$A$1:$AE$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alim_Satim'!$A$1:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taze_Sinyaller'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugun'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tum_Sonuclar'!$A$1:$AE$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alim_Satim'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taze_Sinyaller'!$A$1:$O$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
@@ -515,7 +515,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>OSC_KIRILIM_SON5</t>
+          <t>OSC_KIRILIM_GECEN_SURE</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -586,7 +586,36 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Stochastic(14)</t>
+          </r>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -618,7 +647,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.96</v>
+        <v>24.74</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -648,12 +677,100 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MOM:DİRENÇ↑, OBV:DİRENÇ↑, ROC:DİRENÇ↑</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ROC</t>
+          </r>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑(4b), MOM:DİRENÇ↑, OBV:DİRENÇ↑, ROC:DİRENÇ↑</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Chaikin(7)</t>
+          </r>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -685,7 +802,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -715,12 +832,40 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Stochastic(8)</t>
+          </r>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -752,7 +897,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42.44</v>
+        <v>42.16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -782,12 +927,160 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CCI:DİRENÇ↑, MFI:DESTEK↓, RSI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>RSI</t>
+          </r>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ATR:DESTEK↓(2b), CMO:DESTEK↓(2b), CCI:DİRENÇ↑, MFI:DESTEK↓, MOM:DİRENÇ↑(1b), OBV:DESTEK↓(2b), ROC:DİRENÇ↑(1b), RSI:DESTEK↓, Stochastic:DESTEK↓(4b), Williams %R:DESTEK↓(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(10) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>MACD(10)</t>
+          </r>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -810,7 +1103,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>AKCNS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -819,7 +1112,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87.65000000000001</v>
+        <v>210.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -839,7 +1132,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CCI:HID BEAR</t>
+          <t>Stochastic:HID BEAR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,33 +1142,576 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MOM</t>
+          </r>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ADX:DESTEK↓(2b), CCI:DESTEK↓, Chaikin:DESTEK↓(1b), MOM:DİRENÇ↑(2b), ROC:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(2b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MFI(9)</t>
+          </r>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KARMA</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>DÜŞÜK</t>
+          <t>ORTA</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ACSEL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CCI:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MACD(20)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AKFGY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KIRILIM</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Chaikin</t>
+          </r>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>RSI(7)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>75</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>69</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KIRILIM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Williams %R</t>
+          </r>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(5) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ADX(12)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -886,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -904,14 +1740,14 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="38" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="38" customWidth="1" min="21" max="21"/>
-    <col width="27" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="28" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="38" customWidth="1" min="24" max="24"/>
     <col width="11" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
@@ -1005,7 +1841,7 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>OSC_KIRILIM_SON5</t>
+          <t>OSC_KIRILIM_GECEN_SURE</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -1096,7 +1932,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1150,7 +1986,36 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Chaikin:DİRENÇ↑(2b), Chaikin:DESTEK↓(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Stochastic(14)</t>
+          </r>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1229,7 +2094,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1278,12 +2143,40 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Stochastic(8)</t>
+          </r>
         </is>
       </c>
       <c r="R3" t="n">
@@ -1362,7 +2255,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1411,12 +2304,90 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CCI:DİRENÇ↑(2b), CCI:DESTEK↓, MFI:DİRENÇ↑(4b), MOM:DİRENÇ↑(1b), ROC:DİRENÇ↑(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Chaikin(14)</t>
+          </r>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1495,7 +2466,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87.65000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1544,12 +2515,110 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ADX:DESTEK↓(2b), CCI:DESTEK↓, Chaikin:DESTEK↓(1b), MOM:DİRENÇ↑(2b), ROC:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(2b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MACD(20)</t>
+          </r>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1628,7 +2697,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.96</v>
+        <v>24.74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1677,12 +2746,100 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MOM:DİRENÇ↑, OBV:DİRENÇ↑, ROC:DİRENÇ↑</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ROC</t>
+          </r>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑(4b), MOM:DİRENÇ↑, OBV:DİRENÇ↑, ROC:DİRENÇ↑</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Chaikin(7)</t>
+          </r>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1761,7 +2918,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1810,12 +2967,100 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CCI:DESTEK↓, OBV:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑(1b), CCI:DESTEK↓, Chaikin:DİRENÇ↑(1b), MOM:DİRENÇ↑(1b), OBV:DESTEK↓, ROC:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(2b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(13) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ADX(14)</t>
+          </r>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1894,7 +3139,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.44</v>
+        <v>42.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1943,12 +3188,160 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CCI:DİRENÇ↑, MFI:DESTEK↓, RSI:DESTEK↓</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>RSI</t>
+          </r>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ATR:DESTEK↓(2b), CMO:DESTEK↓(2b), CCI:DİRENÇ↑, MFI:DESTEK↓, MOM:DİRENÇ↑(1b), OBV:DESTEK↓(2b), ROC:DİRENÇ↑(1b), RSI:DESTEK↓, Stochastic:DESTEK↓(4b), Williams %R:DESTEK↓(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(10) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>MACD(10)</t>
+          </r>
         </is>
       </c>
       <c r="R8" t="n">
@@ -2081,7 +3474,106 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>ADX:DESTEK↓(2b), CMO:DİRENÇ↑(2b), CCI:DİRENÇ↑(2b), MACD:DİRENÇ↑(3b), MFI:DESTEK↓(1b), MOM:DİRENÇ↑(2b), ROC:DİRENÇ↑(2b), RSI:DİRENÇ↑(2b), Williams %R:DİRENÇ↑(2b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>ATR(7)</t>
+          </r>
         </is>
       </c>
       <c r="R9" t="n">
@@ -2160,7 +3652,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.77</v>
+        <v>12.54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2209,12 +3701,160 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑, MACD:DİRENÇ↑</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MACD</t>
+          </r>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>ATR:DİRENÇ↑, CMO:DİRENÇ↑(2b), CCI:DİRENÇ↑(2b), MACD:DİRENÇ↑, MFI:DİRENÇ↑(1b), MOM:DİRENÇ↑(2b), OBV:DİRENÇ↑(1b), ROC:DİRENÇ↑(2b), RSI:DİRENÇ↑(2b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(8) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>ADX(20)</t>
+          </r>
         </is>
       </c>
       <c r="R10" t="n">
@@ -2293,7 +3933,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>231</v>
+        <v>231.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2347,7 +3987,136 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>ADX:DESTEK↓(2b), ATR:DESTEK↓(1b), CMO:DİRENÇ↑(2b), CCI:DİRENÇ↑(1b), MACD:DİRENÇ↑(2b), MFI:DESTEK↓(3b), MOM:DİRENÇ↑(3b), OBV:DİRENÇ↑(3b), ROC:DİRENÇ↑(3b), RSI:DİRENÇ↑(2b), Stochastic:DİRENÇ↑(1b), Williams %R:DİRENÇ↑(1b)</t>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Chaikin(7)</t>
+          </r>
         </is>
       </c>
       <c r="R11" t="n">
@@ -2409,8 +4178,2061 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>MFI</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ROC(7)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>ATR, CMO, CCI, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Yatay bant / range</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>8 temas (Güçlü) | 20-10-25 → 08-10-26 | Skor=0.864 [temas 0.8, güncellik 1.0, uzunluk 0.81, fit 0.64, yakınlık 1.0] | Temaslar: 20-10-25, 23-03-26, 30-03-26, 07-04-26, 18-08-26, 27-08-26, 01-10-26, 08-10-26</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 14-05-26 → 18-09-26 | Skor=0.663 [temas 0.714, güncellik 0.958, uzunluk 0.287, fit 0.825, yakınlık 0.265] | Temaslar: 14-05-26, 03-08-26, 09-09-26, 18-09-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>70</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>CCI</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MFI(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Chaikin(15)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>05-10-26</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Stochastic</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 19-08-26 → 30-09-26 | Skor=0.572 [temas 0.6, güncellik 0.958, uzunluk 0.1, fit 0.86, yakınlık 0.096] | Temaslar: 19-08-26, 04-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 21-08-26 → 05-10-26 | Skor=0.680 [temas 0.5, güncellik 1.0, uzunluk 0.103, fit 0.5, yakınlık 1.0] | Temaslar: 21-08-26, 05-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(5) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>OBV(16)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 22-05-26 → 02-10-26 | Skor=0.831 [temas 0.778, güncellik 1.0, uzunluk 0.303, fit 0.657, yakınlık 1.0] | Temaslar: 22-05-26, 10-06-26, 14-07-26, 30-07-26, 06-08-26, 29-09-26, 02-10-26</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 11-09-26 → 29-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.04, fit 0.5, yakınlık 1.0] | Temaslar: 11-09-26, 29-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AHGAZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Chaikin</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(4) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(5) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(5) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>OBV(9)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>25-09-26</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ATR, CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek yukselen, direnç yukselen)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 22-05-26 → 19-08-26 | Skor=0.590 [temas 0.667, güncellik 0.875, uzunluk 0.197, fit 0.848, yakınlık 0.1] | Temaslar: 22-05-26, 10-06-26, 06-08-26, 19-08-26</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 10-08-26 → 25-09-26 | Skor=0.819 [temas 0.714, güncellik 1.0, uzunluk 0.113, fit 0.923, yakınlık 1.0] | Temaslar: 10-08-26, 14-08-26, 07-09-26, 16-09-26, 25-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AHSGY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Williams %R</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>Stochastic(13)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>20</v>
+      </c>
+      <c r="S16" t="n">
+        <v>18</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>15-09-26</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>CCI, MACD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>ADX, CMO, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 13-04-26 → 08-10-26 | Skor=0.768 [temas 0.6, güncellik 1.0, uzunluk 0.403, fit 0.777, yakınlık 1.0] | Temaslar: 13-04-26, 16-04-26, 08-10-26</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 12-05-26 → 15-09-26 | Skor=0.789 [temas 0.667, güncellik 1.0, uzunluk 0.283, fit 0.75, yakınlık 1.0] | Temaslar: 12-05-26, 03-07-26, 08-07-26, 15-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>69</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KIRILIM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Williams %R</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Williams %R(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">RSI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(5) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ADX(12)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 16-09-26 → 08-10-26 | Skor=0.763 [temas 0.6, güncellik 1.0, uzunluk 0.053, fit 0.908, yakınlık 1.0] | Temaslar: 16-09-26, 30-09-26, 08-10-26</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 09-09-26 → 07-10-26 | Skor=0.754 [temas 0.6, güncellik 1.0, uzunluk 0.067, fit 0.809, yakınlık 1.0] | Temaslar: 09-09-26, 22-09-26, 07-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Stochastic:HID BEAR</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MOM</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ROC(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(6) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(9) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>MFI(9)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>08-10-26</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>MOM, OBV, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 24-11-25 → 29-09-26 | Skor=0.829 [temas 0.667, güncellik 1.0, uzunluk 0.707, fit 0.941, yakınlık 1.0] | Temaslar: 24-11-25, 05-12-25, 22-09-26, 29-09-26</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 08-09-26 → 08-10-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.073, fit 0.5, yakınlık 1.0] | Temaslar: 08-09-26, 08-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G19" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Stochastic(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ATR(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(2) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MOM(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>ROC(3)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>CMO, CCI, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 30-03-26 → 08-10-26 | Skor=0.760 [temas 0.6, güncellik 1.0, uzunluk 0.437, fit 0.681, yakınlık 1.0] | Temaslar: 30-03-26, 30-09-26, 08-10-26</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 23-06-26 → 28-08-26 | Skor=0.786 [temas 0.667, güncellik 1.0, uzunluk 0.157, fit 0.78, yakınlık 1.0] | Temaslar: 23-06-26, 17-08-26, 28-08-26, 10-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AKFGY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>75</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>KIRILIM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>Chaikin</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">Chaikin(0) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CCI(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">MACD(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(3) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">CMO(7) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t>RSI(7)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>16</v>
+      </c>
+      <c r="S20" t="n">
+        <v>14</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>21-09-26</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 11-11-25 → 08-10-26 | Skor=0.793 [temas 0.667, güncellik 1.0, uzunluk 0.76, fit 0.549, yakınlık 1.0] | Temaslar: 11-11-25, 31-12-25, 21-09-26, 08-10-26</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 11-09-26 → 05-10-26 | Skor=0.678 [temas 0.5, güncellik 1.0, uzunluk 0.053, fit 0.5, yakınlık 1.0] | Temaslar: 11-09-26, 05-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>70</v>
+      </c>
+      <c r="G21" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0000B050"/>
+            </rPr>
+            <t>▲</t>
+          </r>
+          <r>
+            <t xml:space="preserve">ADX(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t xml:space="preserve">OBV(1) | </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00FF0000"/>
+            </rPr>
+            <t>▼</t>
+          </r>
+          <r>
+            <t>ATR(8)</t>
+          </r>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>CCI, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 17-09-26 → 07-10-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.047, fit 0.5, yakınlık 1.0] | Temaslar: 17-09-26, 07-10-26</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 28-08-26 → 02-10-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.083, fit 0.5, yakınlık 1.0] | Temaslar: 28-08-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AE11"/>
+  <autoFilter ref="A1:AE21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2421,7 +6243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2431,7 +6253,7 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -2537,7 +6359,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>24.96</v>
+        <v>24.74</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -2588,7 +6410,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>231</v>
+        <v>231.2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -2599,7 +6421,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AFYON</t>
+          <t>AKFGY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2616,11 +6438,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chaikin, MFI, OBV</t>
+          <t>CMO, MFI, MOM, RSI, Stochastic, Williams %R</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2630,16 +6452,16 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADX</t>
+          <t>Chaikin</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12.77</v>
+        <v>2.47</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -2650,7 +6472,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADGYO</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2659,7 +6481,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2667,16 +6489,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Williams %R</t>
+          <t>Chaikin, MFI, OBV</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CCI, MOM, ROC, Stochastic</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2686,11 +6508,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ATR, Chaikin</t>
+          <t>ADX</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>42.44</v>
+        <v>12.54</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2701,7 +6523,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>ADGYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2710,7 +6532,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.54</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2718,16 +6540,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ATR, CMO, Chaikin, MACD, MFI, OBV, RSI, Stochastic</t>
+          <t>Williams %R</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CCI, MOM, ROC, Stochastic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2737,11 +6559,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ADX, CCI, MOM, ROC, Williams %R</t>
+          <t>ATR, Chaikin</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18.55</v>
+        <v>42.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -2752,28 +6574,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AGROT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>90.91</v>
+        <v>70</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YÜKSEK</t>
+          <t>ORTA</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MACD</t>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI, Williams %R</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2788,31 +6610,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ADX, ATR, CMO, CCI, Chaikin, MFI, MOM, ROC, RSI, Williams %R</t>
+          <t>CCI, ROC, Stochastic</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8.65</v>
+        <v>1.34</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SATIM</t>
+          <t>ALIM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A1YEN</t>
+          <t>AKFIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2820,16 +6642,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chaikin, MFI</t>
+          <t>ATR, Chaikin</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2839,31 +6661,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADX, ATR, CCI, MACD, RSI, Stochastic, Williams %R</t>
+          <t>CCI, RSI, Williams %R</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.66</v>
+        <v>16.4</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SATIM</t>
+          <t>ALIM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>AKENR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2871,11 +6693,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ATR, CMO, RSI</t>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2890,71 +6712,530 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CCI, MFI, MOM, ROC, Stochastic, Williams %R</t>
+          <t>CMO, CCI, ROC, RSI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4.39</v>
+        <v>7.78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SATIM</t>
+          <t>ALIM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MACD, MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ADX, CCI, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>60</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AHSGY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CCI, MACD</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ADX, CMO, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AHGAZ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ATR, CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AAGYO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CMO, CCI, Chaikin, MFI, MOM, ROC, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ATR, CMO, CCI, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A1YEN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CCI, MACD, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A1CAP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ATR, CMO, RSI</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CCI, MFI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MOM, OBV, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>ADESE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C19" t="n">
         <v>60</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>ORTA</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ADX, Chaikin</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>CCI, MFI, Williams %R</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="J19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>SATIM</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:K19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2965,7 +7246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2979,8 +7260,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="38" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
@@ -3079,7 +7360,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3146,7 +7427,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3213,7 +7494,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.65</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3280,7 +7561,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87.65000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3347,7 +7628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.96</v>
+        <v>24.74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3414,7 +7695,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3481,7 +7762,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.44</v>
+        <v>42.16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -3615,7 +7896,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.77</v>
+        <v>12.54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3682,7 +7963,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>231</v>
+        <v>231.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3732,8 +8013,477 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>33.28</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ATR, CMO, CCI, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>05-10-26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Stochastic</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>69</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>08-10-26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>MOM, OBV, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CMO, CCI, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13-10-26</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>70</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>CCI, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>